--- a/sourcedata/Dim_Speaker.xlsx
+++ b/sourcedata/Dim_Speaker.xlsx
@@ -432,8 +432,8 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
@@ -519,12 +519,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MD. Jessica Johnson</t>
+          <t>DO. Nancy Walker</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PSYCHIATRY</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -543,18 +543,18 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>11101</v>
+        <v>4683</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -570,27 +570,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HCP0008</t>
+          <t>HCP0003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MD. Jennifer Harris</t>
+          <t>DO. Michael Davis</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>NEUROLOGY</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -603,14 +603,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>14005</v>
+        <v>7888</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -626,22 +626,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HCP0014</t>
+          <t>HCP0007</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MD. Matthew Rodriguez</t>
+          <t>DO. Ashley Jackson</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NEUROLOGY</t>
+          <t>PSYCHIATRY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -651,22 +651,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NEXOLID</t>
+          <t>CLAROZEPT,DEPTRAZOL</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>16594</v>
+        <v>17507</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -682,22 +682,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HCP0015</t>
+          <t>HCP0010</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PA. Thomas Wright</t>
+          <t>DO. Daniel Wright</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PSYCHIATRY</t>
+          <t>CARDIOLOGY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -707,22 +707,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>VERITONEX,CLAROZEPT</t>
+          <t>NEXOLID</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>18629</v>
+        <v>11671</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -738,22 +738,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HCP0020</t>
+          <t>HCP0011</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MD. Linda Williams</t>
+          <t>MD. Jennifer Harris</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>INTERNAL MEDICINE</t>
+          <t>NEUROLOGY</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>VERITONEX,CLAROZEPT</t>
+          <t>NEXOLID</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -771,14 +771,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>22767</v>
+        <v>16386</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -794,22 +794,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HCP0022</t>
+          <t>HCP0013</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NP. Michael Martinez</t>
+          <t>MD. Mark Lee</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>NEUROLOGY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -819,22 +819,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NEXOLID,VERITONEX</t>
+          <t>NEXOLID</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
-        <v>8408</v>
+        <v>11668</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -850,12 +850,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HCP0029</t>
+          <t>HCP0017</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NP. Betty Martinez</t>
+          <t>MD. Lisa Harris</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -865,32 +865,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NEXOLID,VERITONEX</t>
+          <t>CLAROZEPT</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K8" t="n">
-        <v>18128</v>
+        <v>22498</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -906,12 +906,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HCP0031</t>
+          <t>HCP0019</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MD. Lisa Johnson</t>
+          <t>NP. James Walker</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -931,22 +931,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NEXOLID,VERITONEX</t>
+          <t>NEXOLID</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>12117</v>
+        <v>17156</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -962,27 +962,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HCP0034</t>
+          <t>HCP0020</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PA. Barbara Garcia</t>
+          <t>PA. Sandra Rodriguez</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FAMILY PRACTICE</t>
+          <t>CARDIOLOGY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -991,18 +991,18 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>4016</v>
+        <v>8740</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1018,22 +1018,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HCP0035</t>
+          <t>HCP0021</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MD. Patricia King</t>
+          <t>PharmD. Matthew Garcia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>NEUROLOGY</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1047,18 +1047,18 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>21480</v>
+        <v>13921</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HCP0036</t>
+          <t>HCP0026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NP. Daniel Anderson</t>
+          <t>PA. Christopher Thomas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>VERITONEX,CLAROZEPT</t>
+          <t>CLAROZEPT,DEPTRAZOL</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K12" t="n">
-        <v>8366</v>
+        <v>4202</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1130,47 +1130,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HCP0040</t>
+          <t>HCP0027</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PA. Susan Hall</t>
+          <t>DO. David Smith</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NEUROLOGY</t>
+          <t>PSYCHIATRY</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NEXOLID</t>
+          <t>DEPTRAZOL</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K13" t="n">
-        <v>22401</v>
+        <v>18138</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
